--- a/grupos/5AEM - Estadisticos 20241.xlsx
+++ b/grupos/5AEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="87">
   <si>
     <t>Materia</t>
   </si>
@@ -182,21 +182,21 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>Hernandez Alonso Antonio Ascari</t>
   </si>
   <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Marin Arzaba Roberto</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -209,43 +209,70 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>PANZO</t>
   </si>
   <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>MACARIO</t>
   </si>
   <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
     <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
   </si>
   <si>
     <t>GABAEL</t>
@@ -778,25 +805,25 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -867,25 +894,25 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -909,13 +936,13 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z5">
         <v>8</v>
@@ -927,7 +954,7 @@
         <v>9</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -956,25 +983,25 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1001,22 +1028,22 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1045,25 +1072,25 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1090,10 +1117,10 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>8</v>
@@ -1102,7 +1129,7 @@
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1134,25 +1161,25 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1182,19 +1209,19 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB8">
         <v>10</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1223,25 +1250,25 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1268,22 +1295,22 @@
         <v>5</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1312,25 +1339,25 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1354,10 +1381,10 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1366,10 +1393,10 @@
         <v>9</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>9</v>
@@ -1401,25 +1428,25 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1446,10 +1473,10 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1490,25 +1517,25 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1535,22 +1562,22 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>9</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB12">
         <v>10</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1579,25 +1606,25 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1624,19 +1651,19 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC13">
         <v>7</v>
@@ -1668,25 +1695,25 @@
         <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1713,19 +1740,19 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>6</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1757,25 +1784,25 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1802,7 +1829,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1811,13 +1838,13 @@
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1846,25 +1873,25 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1888,7 +1915,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -1900,13 +1927,13 @@
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1935,25 +1962,25 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1980,16 +2007,16 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>10</v>
@@ -2024,25 +2051,25 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2069,22 +2096,22 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2113,25 +2140,25 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2158,10 +2185,10 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>8</v>
@@ -2202,25 +2229,25 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2250,7 +2277,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z20">
         <v>10</v>
@@ -2262,7 +2289,7 @@
         <v>10</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2291,25 +2318,25 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2336,7 +2363,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2345,13 +2372,13 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2380,25 +2407,25 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2425,16 +2452,16 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>7</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB22">
         <v>10</v>
@@ -2469,25 +2496,25 @@
         <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2514,16 +2541,16 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2558,25 +2585,25 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2600,10 +2627,10 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2612,13 +2639,13 @@
         <v>8</v>
       </c>
       <c r="AA24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2647,25 +2674,25 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2692,7 +2719,7 @@
         <v>7</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2736,25 +2763,25 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2778,10 +2805,10 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2825,25 +2852,25 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2879,13 +2906,13 @@
         <v>7</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2914,25 +2941,25 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2956,7 +2983,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2971,10 +2998,10 @@
         <v>7</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3003,25 +3030,25 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3048,7 +3075,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -3060,10 +3087,10 @@
         <v>10</v>
       </c>
       <c r="AB29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3092,25 +3119,25 @@
         <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3134,13 +3161,13 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>9</v>
@@ -3152,7 +3179,7 @@
         <v>10</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3181,25 +3208,25 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3223,7 +3250,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -3235,13 +3262,13 @@
         <v>7</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB31">
         <v>10</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3478,7 +3505,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3499,7 +3526,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3735,10 +3762,10 @@
         <v>80</v>
       </c>
       <c r="J9">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L9">
         <v>91.3</v>
@@ -3756,10 +3783,10 @@
         <v>80</v>
       </c>
       <c r="Q9">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S9">
         <v>91.3</v>
@@ -3868,10 +3895,10 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J11">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3889,10 +3916,10 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q11">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -3939,7 +3966,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -3960,7 +3987,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4004,7 +4031,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -4025,7 +4052,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4075,7 +4102,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -4096,7 +4123,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4140,13 +4167,13 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J15">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L15">
         <v>91.3</v>
@@ -4161,13 +4188,13 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q15">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="R15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S15">
         <v>91.3</v>
@@ -4226,7 +4253,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4247,7 +4274,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4276,7 +4303,7 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -4297,7 +4324,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4344,13 +4371,13 @@
         <v>80</v>
       </c>
       <c r="I18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J18">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L18">
         <v>91.3</v>
@@ -4362,16 +4389,16 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q18">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="R18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S18">
         <v>91.3</v>
@@ -4383,7 +4410,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4548,13 +4575,13 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J21">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L21">
         <v>91.3</v>
@@ -4569,13 +4596,13 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q21">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S21">
         <v>91.3</v>
@@ -4684,10 +4711,10 @@
         <v>85</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J23">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -4702,13 +4729,13 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q23">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -4723,7 +4750,7 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4752,10 +4779,10 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J24">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -4773,10 +4800,10 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q24">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4823,7 +4850,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -4844,7 +4871,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -4959,7 +4986,7 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4980,7 +5007,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5030,7 +5057,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5051,7 +5078,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5228,10 +5255,10 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J31">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -5249,10 +5276,10 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q31">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5356,7 +5383,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -5365,19 +5392,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>82.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="G3" s="2">
-        <v>17.9</v>
+        <v>14.3</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5388,7 +5415,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -5397,19 +5424,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="G4" s="2">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5423,25 +5450,25 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5">
         <v>28</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>89.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5452,7 +5479,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -5461,19 +5488,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>89.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5484,7 +5511,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -5493,19 +5520,19 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5516,7 +5543,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>58</v>
@@ -5525,19 +5552,19 @@
         <v>28</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5587,7 +5614,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5619,22 +5646,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920013</v>
+        <v>22330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5642,22 +5669,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920013</v>
+        <v>22330051920003</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5665,22 +5692,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920015</v>
+        <v>22330051920006</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5688,22 +5715,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920015</v>
+        <v>22330051920006</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5711,16 +5738,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920003</v>
+        <v>22330051920015</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -5734,22 +5761,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920320</v>
+        <v>22330051920015</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5757,24 +5784,162 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
+        <v>22330051920017</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920017</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920382</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920382</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920013</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920320</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
         <v>22330051920322</v>
       </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
         <v>53</v>
       </c>
-      <c r="G8">
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEM - Estadisticos 20241.xlsx
+++ b/grupos/5AEM - Estadisticos 20241.xlsx
@@ -179,7 +179,7 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
+    <t>Martínez Sota Luis Rey</t>
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>

--- a/grupos/5AEM - Estadisticos 20241.xlsx
+++ b/grupos/5AEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -218,21 +218,15 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
@@ -242,21 +236,15 @@
     <t>QUERO</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
     <t>JERONIMO</t>
   </si>
   <si>
     <t>ZARATE</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
     <t>DANIEL</t>
   </si>
   <si>
@@ -266,19 +254,13 @@
     <t>DIEGO JESUS</t>
   </si>
   <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
     <t>LUIS</t>
   </si>
   <si>
     <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
   </si>
 </sst>
 </file>
@@ -814,7 +796,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -903,7 +885,7 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>9</v>
@@ -992,7 +974,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -1081,7 +1063,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1123,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -1170,7 +1152,7 @@
         <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1212,7 +1194,7 @@
         <v>8</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -1259,7 +1241,7 @@
         <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1348,7 +1330,7 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1437,7 +1419,7 @@
         <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1526,7 +1508,7 @@
         <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1615,7 +1597,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1704,7 +1686,7 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1746,7 +1728,7 @@
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -1793,7 +1775,7 @@
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1882,7 +1864,7 @@
         <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -1924,7 +1906,7 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>9</v>
@@ -1971,7 +1953,7 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>9</v>
@@ -2013,7 +1995,7 @@
         <v>8</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -2060,7 +2042,7 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -2102,7 +2084,7 @@
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2149,7 +2131,7 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>7</v>
@@ -2238,7 +2220,7 @@
         <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2327,7 +2309,7 @@
         <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -2369,7 +2351,7 @@
         <v>6</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>7</v>
@@ -2416,7 +2398,7 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2505,7 +2487,7 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2547,7 +2529,7 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>8</v>
@@ -2594,7 +2576,7 @@
         <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -2683,7 +2665,7 @@
         <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -2725,7 +2707,7 @@
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>9</v>
@@ -2772,7 +2754,7 @@
         <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -2861,7 +2843,7 @@
         <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -2903,7 +2885,7 @@
         <v>9</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>9</v>
@@ -2950,7 +2932,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>6</v>
@@ -3039,7 +3021,7 @@
         <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -3128,7 +3110,7 @@
         <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3217,7 +3199,7 @@
         <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>9</v>
@@ -3564,7 +3546,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>91.3</v>
+        <v>93</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -3585,7 +3567,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>91.3</v>
+        <v>93</v>
       </c>
       <c r="T6">
         <v>100</v>
@@ -3768,7 +3750,7 @@
         <v>97.5</v>
       </c>
       <c r="L9">
-        <v>91.3</v>
+        <v>90.7</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -3789,7 +3771,7 @@
         <v>97.5</v>
       </c>
       <c r="S9">
-        <v>91.3</v>
+        <v>90.7</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -3904,7 +3886,7 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>91.3</v>
+        <v>90.7</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -3925,7 +3907,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>91.3</v>
+        <v>90.7</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4040,7 +4022,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>91.3</v>
+        <v>93</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -4061,7 +4043,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>91.3</v>
+        <v>93</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -4176,7 +4158,7 @@
         <v>97.5</v>
       </c>
       <c r="L15">
-        <v>91.3</v>
+        <v>90.7</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -4197,7 +4179,7 @@
         <v>97.5</v>
       </c>
       <c r="S15">
-        <v>91.3</v>
+        <v>90.7</v>
       </c>
       <c r="T15">
         <v>100</v>
@@ -4380,7 +4362,7 @@
         <v>97.5</v>
       </c>
       <c r="L18">
-        <v>91.3</v>
+        <v>95.3</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -4401,7 +4383,7 @@
         <v>97.5</v>
       </c>
       <c r="S18">
-        <v>91.3</v>
+        <v>95.3</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -4584,7 +4566,7 @@
         <v>97.5</v>
       </c>
       <c r="L21">
-        <v>91.3</v>
+        <v>95.3</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -4605,7 +4587,7 @@
         <v>97.5</v>
       </c>
       <c r="S21">
-        <v>91.3</v>
+        <v>95.3</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -4720,7 +4702,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>91.3</v>
+        <v>90.7</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -4741,7 +4723,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>91.3</v>
+        <v>90.7</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -4788,7 +4770,7 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -4809,7 +4791,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5360,19 +5342,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>67.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>32.1</v>
+        <v>17.9</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5614,7 +5596,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5652,10 +5634,10 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5675,10 +5657,10 @@
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5698,10 +5680,10 @@
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5721,10 +5703,10 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -5744,10 +5726,10 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -5767,10 +5749,10 @@
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5784,22 +5766,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920017</v>
+        <v>22330051920013</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5810,19 +5792,19 @@
         <v>22330051920017</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5833,13 +5815,13 @@
         <v>22330051920382</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5848,98 +5830,6 @@
         <v>54</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920382</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920013</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920320</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920322</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEM - Estadisticos 20241.xlsx
+++ b/grupos/5AEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -128,6 +128,9 @@
     <t>RIOS GALVAN GABRIEL</t>
   </si>
   <si>
+    <t>ROMERO CAMPOS GREGORIO</t>
+  </si>
+  <si>
     <t>ROMERO GILES SAUL AZAEL</t>
   </si>
   <si>
@@ -207,6 +210,15 @@
   </si>
   <si>
     <t>Nombres</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
   </si>
   <si>
     <t>APALE</t>
@@ -622,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -811,7 +823,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -900,7 +912,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -989,7 +1001,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1078,7 +1090,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1167,7 +1179,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1256,7 +1268,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1345,7 +1357,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1434,7 +1446,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1523,7 +1535,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1544,7 +1556,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1612,7 +1624,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1701,7 +1713,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1722,7 +1734,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1790,7 +1802,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1879,7 +1891,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1900,7 +1912,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1968,7 +1980,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2057,7 +2069,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2078,7 +2090,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2146,7 +2158,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2167,7 +2179,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2235,7 +2247,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2324,7 +2336,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2413,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2434,7 +2446,7 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2502,7 +2514,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2523,7 +2535,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2591,7 +2603,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2680,7 +2692,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2769,7 +2781,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2813,46 +2825,46 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="E27">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="G27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H27">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="I27">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="J27">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="K27">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="L27">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="M27">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="N27">
         <v>10</v>
       </c>
       <c r="O27">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2870,31 +2882,31 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="AA27">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="AB27">
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2902,52 +2914,52 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28">
         <v>9</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>7</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M28">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2971,19 +2983,19 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -2994,49 +3006,49 @@
         <v>9</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H29">
         <v>10</v>
       </c>
       <c r="I29">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3054,25 +3066,25 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3083,25 +3095,25 @@
         <v>9</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30">
         <v>10</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>10</v>
@@ -3110,7 +3122,7 @@
         <v>7</v>
       </c>
       <c r="L30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3125,7 +3137,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3143,16 +3155,16 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <v>10</v>
@@ -3161,7 +3173,7 @@
         <v>10</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3169,52 +3181,52 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>9</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>10</v>
       </c>
       <c r="H31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>10</v>
       </c>
       <c r="O31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3232,24 +3244,113 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>8</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB31">
         <v>10</v>
       </c>
       <c r="AC31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>9</v>
+      </c>
+      <c r="D32">
+        <v>8</v>
+      </c>
+      <c r="E32">
+        <v>7</v>
+      </c>
+      <c r="F32">
+        <v>7</v>
+      </c>
+      <c r="G32">
+        <v>10</v>
+      </c>
+      <c r="H32">
+        <v>10</v>
+      </c>
+      <c r="I32">
+        <v>8</v>
+      </c>
+      <c r="J32">
+        <v>9</v>
+      </c>
+      <c r="K32">
+        <v>8</v>
+      </c>
+      <c r="L32">
+        <v>7</v>
+      </c>
+      <c r="M32">
+        <v>9</v>
+      </c>
+      <c r="N32">
+        <v>10</v>
+      </c>
+      <c r="O32">
+        <v>5</v>
+      </c>
+      <c r="P32">
+        <v>-1</v>
+      </c>
+      <c r="Q32">
+        <v>9</v>
+      </c>
+      <c r="R32">
+        <v>-1</v>
+      </c>
+      <c r="S32">
+        <v>-1</v>
+      </c>
+      <c r="T32">
+        <v>-1</v>
+      </c>
+      <c r="U32">
+        <v>-1</v>
+      </c>
+      <c r="V32">
+        <v>-1</v>
+      </c>
+      <c r="W32">
+        <v>7</v>
+      </c>
+      <c r="X32">
+        <v>9</v>
+      </c>
+      <c r="Y32">
+        <v>8</v>
+      </c>
+      <c r="Z32">
+        <v>7</v>
+      </c>
+      <c r="AA32">
+        <v>8</v>
+      </c>
+      <c r="AB32">
+        <v>10</v>
+      </c>
+      <c r="AC32">
         <v>8</v>
       </c>
     </row>
@@ -3266,7 +3367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3275,7 +3376,7 @@
     <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3284,7 +3385,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -3293,7 +3394,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -3437,7 +3538,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -3505,7 +3606,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V5">
         <v>88.59999999999999</v>
@@ -3573,7 +3674,7 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -3641,7 +3742,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3709,7 +3810,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3765,7 +3866,7 @@
         <v>80</v>
       </c>
       <c r="Q9">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R9">
         <v>97.5</v>
@@ -3777,7 +3878,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3845,7 +3946,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -3901,7 +4002,7 @@
         <v>85</v>
       </c>
       <c r="Q11">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -3913,7 +4014,7 @@
         <v>100</v>
       </c>
       <c r="U11">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -3969,7 +4070,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -3981,7 +4082,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4049,7 +4150,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4105,7 +4206,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4117,7 +4218,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4173,7 +4274,7 @@
         <v>85</v>
       </c>
       <c r="Q15">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="R15">
         <v>97.5</v>
@@ -4185,7 +4286,7 @@
         <v>100</v>
       </c>
       <c r="U15">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -4253,7 +4354,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V16">
         <v>93.2</v>
@@ -4321,7 +4422,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4377,7 +4478,7 @@
         <v>85</v>
       </c>
       <c r="Q18">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R18">
         <v>97.5</v>
@@ -4389,7 +4490,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V18">
         <v>90.90000000000001</v>
@@ -4457,7 +4558,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4525,7 +4626,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4581,7 +4682,7 @@
         <v>90</v>
       </c>
       <c r="Q21">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R21">
         <v>97.5</v>
@@ -4593,7 +4694,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4661,7 +4762,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4717,7 +4818,7 @@
         <v>95</v>
       </c>
       <c r="Q23">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -4729,7 +4830,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V23">
         <v>93.2</v>
@@ -4785,7 +4886,7 @@
         <v>90</v>
       </c>
       <c r="Q24">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4797,7 +4898,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -4853,7 +4954,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -4865,7 +4966,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -4933,7 +5034,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -4944,67 +5045,67 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>100</v>
       </c>
       <c r="H27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N27">
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U27">
         <v>100</v>
       </c>
       <c r="V27">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5015,10 +5116,10 @@
         <v>100</v>
       </c>
       <c r="C28">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D28">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -5036,10 +5137,10 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K28">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5057,10 +5158,10 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R28">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5069,7 +5170,7 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5086,7 +5187,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -5107,7 +5208,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -5128,7 +5229,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -5137,7 +5238,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5205,7 +5306,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5219,63 +5320,131 @@
         <v>100</v>
       </c>
       <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31">
+        <v>100</v>
+      </c>
+      <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="G31">
+        <v>100</v>
+      </c>
+      <c r="H31">
+        <v>100</v>
+      </c>
+      <c r="I31">
+        <v>100</v>
+      </c>
+      <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
+        <v>100</v>
+      </c>
+      <c r="O31">
+        <v>100</v>
+      </c>
+      <c r="P31">
+        <v>100</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
+        <v>100</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
+        <v>100</v>
+      </c>
+      <c r="U31">
+        <v>66.7</v>
+      </c>
+      <c r="V31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
+      <c r="A32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32">
+        <v>100</v>
+      </c>
+      <c r="C32">
         <v>92</v>
       </c>
-      <c r="D31">
-        <v>100</v>
-      </c>
-      <c r="E31">
-        <v>100</v>
-      </c>
-      <c r="F31">
-        <v>100</v>
-      </c>
-      <c r="G31">
-        <v>100</v>
-      </c>
-      <c r="H31">
-        <v>100</v>
-      </c>
-      <c r="I31">
+      <c r="D32">
+        <v>100</v>
+      </c>
+      <c r="E32">
+        <v>100</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32">
+        <v>100</v>
+      </c>
+      <c r="H32">
+        <v>100</v>
+      </c>
+      <c r="I32">
         <v>95</v>
       </c>
-      <c r="J31">
+      <c r="J32">
         <v>96</v>
       </c>
-      <c r="K31">
-        <v>100</v>
-      </c>
-      <c r="L31">
-        <v>100</v>
-      </c>
-      <c r="M31">
-        <v>100</v>
-      </c>
-      <c r="N31">
-        <v>100</v>
-      </c>
-      <c r="O31">
-        <v>100</v>
-      </c>
-      <c r="P31">
+      <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
+        <v>100</v>
+      </c>
+      <c r="M32">
+        <v>100</v>
+      </c>
+      <c r="N32">
+        <v>100</v>
+      </c>
+      <c r="O32">
+        <v>100</v>
+      </c>
+      <c r="P32">
         <v>95</v>
       </c>
-      <c r="Q31">
-        <v>96</v>
-      </c>
-      <c r="R31">
-        <v>100</v>
-      </c>
-      <c r="S31">
-        <v>100</v>
-      </c>
-      <c r="T31">
-        <v>100</v>
-      </c>
-      <c r="U31">
-        <v>100</v>
-      </c>
-      <c r="V31">
+      <c r="Q32">
+        <v>97.5</v>
+      </c>
+      <c r="R32">
+        <v>100</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
+      </c>
+      <c r="T32">
+        <v>100</v>
+      </c>
+      <c r="U32">
+        <v>66.7</v>
+      </c>
+      <c r="V32">
         <v>100</v>
       </c>
     </row>
@@ -5304,31 +5473,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5336,10 +5505,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>23</v>
@@ -5348,19 +5517,19 @@
         <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>82.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="G2" s="2">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="H2">
         <v>7.4</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5368,10 +5537,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>24</v>
@@ -5380,19 +5549,19 @@
         <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="G3" s="2">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="H3">
         <v>7.6</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5400,10 +5569,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>25</v>
@@ -5412,30 +5581,30 @@
         <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>89.3</v>
+        <v>86.2</v>
       </c>
       <c r="G4" s="2">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="H4">
         <v>8.300000000000001</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>27</v>
@@ -5444,45 +5613,45 @@
         <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>96.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6">
+        <v>29</v>
+      </c>
+      <c r="D6">
         <v>28</v>
-      </c>
-      <c r="D6">
-        <v>27</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>96.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5496,10 +5665,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>28</v>
@@ -5508,19 +5677,19 @@
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5528,10 +5697,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8">
         <v>28</v>
@@ -5540,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
@@ -5549,10 +5718,10 @@
         <v>7.6</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>
@@ -5562,7 +5731,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5571,22 +5740,142 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>22330051920326</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>22330051920326</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>22330051920326</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>22330051920326</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>22330051920326</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>22330051920326</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -5605,22 +5894,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -5631,19 +5920,19 @@
         <v>22330051920003</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5654,19 +5943,19 @@
         <v>22330051920003</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5677,19 +5966,19 @@
         <v>22330051920006</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5700,19 +5989,19 @@
         <v>22330051920006</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5723,19 +6012,19 @@
         <v>22330051920015</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5746,19 +6035,19 @@
         <v>22330051920015</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5769,19 +6058,19 @@
         <v>22330051920013</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5792,19 +6081,19 @@
         <v>22330051920017</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5815,19 +6104,19 @@
         <v>22330051920382</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>

--- a/grupos/5AEM - Estadisticos 20241.xlsx
+++ b/grupos/5AEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -191,15 +191,15 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Hernandez Alonso Antonio Ascari</t>
+  </si>
+  <si>
+    <t>Marin Arzaba Roberto</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Hernandez Alonso Antonio Ascari</t>
-  </si>
-  <si>
-    <t>Marin Arzaba Roberto</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,6 +221,9 @@
     <t>GREGORIO</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -239,6 +242,9 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
@@ -255,6 +261,9 @@
   </si>
   <si>
     <t>ZARATE</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>DANIEL</t>
@@ -826,7 +835,7 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -838,7 +847,7 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -859,7 +868,7 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -915,7 +924,7 @@
         <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -927,7 +936,7 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -948,7 +957,7 @@
         <v>9</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1004,7 +1013,7 @@
         <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1016,7 +1025,7 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1093,7 +1102,7 @@
         <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1105,7 +1114,7 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1114,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z7">
         <v>9</v>
@@ -1126,7 +1135,7 @@
         <v>10</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1182,7 +1191,7 @@
         <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1194,7 +1203,7 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1271,7 +1280,7 @@
         <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1283,7 +1292,7 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1304,7 +1313,7 @@
         <v>6</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1360,7 +1369,7 @@
         <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1372,7 +1381,7 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1393,7 +1402,7 @@
         <v>9</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1449,7 +1458,7 @@
         <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1461,7 +1470,7 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1482,7 +1491,7 @@
         <v>5</v>
       </c>
       <c r="AC11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1538,7 +1547,7 @@
         <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1550,7 +1559,7 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1627,7 +1636,7 @@
         <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1639,7 +1648,7 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1648,7 +1657,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1716,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1728,7 +1737,7 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1805,7 +1814,7 @@
         <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1817,7 +1826,7 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1894,7 +1903,7 @@
         <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1906,7 +1915,7 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1927,7 +1936,7 @@
         <v>9</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1983,7 +1992,7 @@
         <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1995,7 +2004,7 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -2004,7 +2013,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -2072,7 +2081,7 @@
         <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2084,7 +2093,7 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2093,7 +2102,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z18">
         <v>6</v>
@@ -2161,7 +2170,7 @@
         <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2173,7 +2182,7 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2182,7 +2191,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z19">
         <v>8</v>
@@ -2250,7 +2259,7 @@
         <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2262,7 +2271,7 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2271,7 +2280,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z20">
         <v>10</v>
@@ -2339,7 +2348,7 @@
         <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2351,7 +2360,7 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2360,7 +2369,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>7</v>
@@ -2372,7 +2381,7 @@
         <v>7</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2428,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2440,7 +2449,7 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2461,7 +2470,7 @@
         <v>10</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2517,7 +2526,7 @@
         <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2529,7 +2538,7 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2538,7 +2547,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>6</v>
@@ -2550,7 +2559,7 @@
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2606,7 +2615,7 @@
         <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2618,7 +2627,7 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2695,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2707,7 +2716,7 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2784,7 +2793,7 @@
         <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2796,7 +2805,7 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2962,7 +2971,7 @@
         <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2974,7 +2983,7 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -3051,7 +3060,7 @@
         <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3063,7 +3072,7 @@
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3084,7 +3093,7 @@
         <v>8</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3140,7 +3149,7 @@
         <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3152,7 +3161,7 @@
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3173,7 +3182,7 @@
         <v>10</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3229,7 +3238,7 @@
         <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3241,7 +3250,7 @@
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3250,7 +3259,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z31">
         <v>9</v>
@@ -3318,7 +3327,7 @@
         <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3330,7 +3339,7 @@
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>7</v>
@@ -3597,7 +3606,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3609,7 +3618,7 @@
         <v>66.7</v>
       </c>
       <c r="V5">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3869,7 +3878,7 @@
         <v>97.5</v>
       </c>
       <c r="R9">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S9">
         <v>90.7</v>
@@ -3881,7 +3890,7 @@
         <v>66.7</v>
       </c>
       <c r="V9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4005,7 +4014,7 @@
         <v>95</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S11">
         <v>90.7</v>
@@ -4017,7 +4026,7 @@
         <v>66.7</v>
       </c>
       <c r="V11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4277,7 +4286,7 @@
         <v>96.3</v>
       </c>
       <c r="R15">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S15">
         <v>90.7</v>
@@ -4289,7 +4298,7 @@
         <v>66.7</v>
       </c>
       <c r="V15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4345,7 +4354,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4357,7 +4366,7 @@
         <v>66.7</v>
       </c>
       <c r="V16">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4481,7 +4490,7 @@
         <v>95</v>
       </c>
       <c r="R18">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S18">
         <v>95.3</v>
@@ -4493,7 +4502,7 @@
         <v>66.7</v>
       </c>
       <c r="V18">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4685,7 +4694,7 @@
         <v>97.5</v>
       </c>
       <c r="R21">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S21">
         <v>95.3</v>
@@ -4765,7 +4774,7 @@
         <v>66.7</v>
       </c>
       <c r="V22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4833,7 +4842,7 @@
         <v>66.7</v>
       </c>
       <c r="V23">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4901,7 +4910,7 @@
         <v>66.7</v>
       </c>
       <c r="V24">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5229,7 +5238,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -5241,7 +5250,7 @@
         <v>66.7</v>
       </c>
       <c r="V29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5598,42 +5607,42 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5">
         <v>29</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>93.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G5" s="2">
         <v>3.4</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6">
         <v>29</v>
@@ -5642,27 +5651,27 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
         <v>96.59999999999999</v>
       </c>
       <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>8.4</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
         <v>3.4</v>
-      </c>
-      <c r="H6">
-        <v>8.9</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -5683,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5694,7 +5703,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>59</v>
@@ -5715,7 +5724,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -5795,7 +5804,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5835,7 +5844,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5875,7 +5884,7 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -5885,7 +5894,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5917,22 +5926,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920003</v>
+        <v>22330051920010</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5940,22 +5949,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920003</v>
+        <v>22330051920010</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5963,22 +5972,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920006</v>
+        <v>22330051920010</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5986,22 +5995,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920006</v>
+        <v>22330051920010</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
         <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6009,16 +6018,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920015</v>
+        <v>22330051920003</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
         <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6032,16 +6041,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920015</v>
+        <v>22330051920003</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
         <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -6055,22 +6064,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920013</v>
+        <v>22330051920006</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
         <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6078,22 +6087,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920017</v>
+        <v>22330051920006</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
         <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6101,24 +6110,116 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920382</v>
+        <v>22330051920015</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
         <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920015</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920013</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920017</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
         <v>55</v>
       </c>
-      <c r="G10">
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920382</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEM - Estadisticos 20241.xlsx
+++ b/grupos/5AEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="70">
   <si>
     <t>Materia</t>
   </si>
@@ -185,12 +185,12 @@
     <t>Martínez Sota Luis Rey</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Hernandez Alonso Antonio Ascari</t>
   </si>
   <si>
@@ -212,76 +212,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>COYOHUA</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>EDER</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
     <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
   </si>
 </sst>
 </file>
@@ -829,7 +775,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -838,13 +784,13 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -918,7 +864,7 @@
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>8</v>
@@ -927,19 +873,19 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>7</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -954,7 +900,7 @@
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>7</v>
@@ -1007,7 +953,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>6</v>
@@ -1016,19 +962,19 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>8</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1037,13 +983,13 @@
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -1096,7 +1042,7 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1105,13 +1051,13 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1126,7 +1072,7 @@
         <v>9</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -1185,7 +1131,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>8</v>
@@ -1194,13 +1140,13 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1218,7 +1164,7 @@
         <v>7</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB8">
         <v>10</v>
@@ -1274,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -1283,19 +1229,19 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1304,7 +1250,7 @@
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA9">
         <v>6</v>
@@ -1363,7 +1309,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1372,19 +1318,19 @@
         <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>8</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1452,7 +1398,7 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1461,19 +1407,19 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>7</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1485,10 +1431,10 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>6</v>
@@ -1541,7 +1487,7 @@
         <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>7</v>
@@ -1550,13 +1496,13 @@
         <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1571,7 +1517,7 @@
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>9</v>
@@ -1630,7 +1576,7 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>6</v>
@@ -1639,19 +1585,19 @@
         <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>7</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1719,7 +1665,7 @@
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -1728,13 +1674,13 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1808,7 +1754,7 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1817,13 +1763,13 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1838,10 +1784,10 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB15">
         <v>7</v>
@@ -1897,7 +1843,7 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1906,13 +1852,13 @@
         <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1930,10 +1876,10 @@
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>8</v>
@@ -1986,7 +1932,7 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -1995,19 +1941,19 @@
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>10</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -2075,7 +2021,7 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>9</v>
@@ -2084,19 +2030,19 @@
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>6</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2164,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -2173,19 +2119,19 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>10</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2194,13 +2140,13 @@
         <v>7</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>9</v>
@@ -2253,7 +2199,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2262,13 +2208,13 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2342,7 +2288,7 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -2351,19 +2297,19 @@
         <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>5</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2372,13 +2318,13 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>7</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC21">
         <v>6</v>
@@ -2431,7 +2377,7 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>8</v>
@@ -2440,19 +2386,19 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>7</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2461,7 +2407,7 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2520,7 +2466,7 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>8</v>
@@ -2529,19 +2475,19 @@
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>8</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2550,10 +2496,10 @@
         <v>8</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2609,7 +2555,7 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2618,13 +2564,13 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2642,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB24">
         <v>10</v>
@@ -2698,7 +2644,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>9</v>
@@ -2707,13 +2653,13 @@
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2731,7 +2677,7 @@
         <v>7</v>
       </c>
       <c r="AA25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB25">
         <v>9</v>
@@ -2787,7 +2733,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -2796,13 +2742,13 @@
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2834,88 +2780,88 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB27">
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2965,7 +2911,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2974,19 +2920,19 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>10</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -3054,7 +3000,7 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -3063,19 +3009,19 @@
         <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>5</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -3087,10 +3033,10 @@
         <v>7</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>7</v>
@@ -3143,7 +3089,7 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -3152,13 +3098,13 @@
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>8</v>
@@ -3179,7 +3125,7 @@
         <v>10</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3232,7 +3178,7 @@
         <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -3241,13 +3187,13 @@
         <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3321,7 +3267,7 @@
         <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
         <v>9</v>
@@ -3330,13 +3276,13 @@
         <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>8</v>
@@ -3354,7 +3300,7 @@
         <v>7</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB32">
         <v>10</v>
@@ -3532,7 +3478,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3547,7 +3493,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -3600,7 +3546,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3609,13 +3555,13 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="T5">
         <v>100</v>
       </c>
       <c r="U5">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V5">
         <v>92.2</v>
@@ -3668,7 +3614,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3677,13 +3623,13 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>93</v>
+        <v>92.2</v>
       </c>
       <c r="T6">
         <v>100</v>
       </c>
       <c r="U6">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -3751,7 +3697,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3804,7 +3750,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3819,7 +3765,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3872,7 +3818,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q9">
         <v>97.5</v>
@@ -3881,13 +3827,13 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S9">
-        <v>90.7</v>
+        <v>93.8</v>
       </c>
       <c r="T9">
         <v>100</v>
       </c>
       <c r="U9">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V9">
         <v>96.90000000000001</v>
@@ -3955,7 +3901,7 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -4008,7 +3954,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q11">
         <v>95</v>
@@ -4017,13 +3963,13 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S11">
-        <v>90.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T11">
         <v>100</v>
       </c>
       <c r="U11">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V11">
         <v>96.90000000000001</v>
@@ -4091,7 +4037,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4144,7 +4090,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4153,13 +4099,13 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>93</v>
+        <v>95.3</v>
       </c>
       <c r="T13">
         <v>100</v>
       </c>
       <c r="U13">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4212,7 +4158,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q14">
         <v>97.5</v>
@@ -4227,7 +4173,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4280,7 +4226,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q15">
         <v>96.3</v>
@@ -4289,13 +4235,13 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S15">
-        <v>90.7</v>
+        <v>93.8</v>
       </c>
       <c r="T15">
         <v>100</v>
       </c>
       <c r="U15">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V15">
         <v>96.90000000000001</v>
@@ -4348,7 +4294,7 @@
         <v>93.2</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4363,7 +4309,7 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V16">
         <v>95.3</v>
@@ -4416,7 +4362,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4431,7 +4377,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4484,7 +4430,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P18">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q18">
         <v>95</v>
@@ -4499,7 +4445,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V18">
         <v>90.59999999999999</v>
@@ -4552,7 +4498,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4561,13 +4507,13 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T19">
         <v>100</v>
       </c>
       <c r="U19">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4635,7 +4581,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4688,7 +4634,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q21">
         <v>97.5</v>
@@ -4697,13 +4643,13 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S21">
-        <v>95.3</v>
+        <v>93.8</v>
       </c>
       <c r="T21">
         <v>100</v>
       </c>
       <c r="U21">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4756,7 +4702,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4765,13 +4711,13 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T22">
         <v>100</v>
       </c>
       <c r="U22">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V22">
         <v>96.90000000000001</v>
@@ -4824,7 +4770,7 @@
         <v>93.2</v>
       </c>
       <c r="P23">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Q23">
         <v>97.5</v>
@@ -4833,13 +4779,13 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>90.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T23">
         <v>100</v>
       </c>
       <c r="U23">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V23">
         <v>92.2</v>
@@ -4892,7 +4838,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q24">
         <v>96.3</v>
@@ -4901,13 +4847,13 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="T24">
         <v>100</v>
       </c>
       <c r="U24">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V24">
         <v>96.90000000000001</v>
@@ -4960,7 +4906,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q25">
         <v>98.8</v>
@@ -4969,13 +4915,13 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T25">
         <v>100</v>
       </c>
       <c r="U25">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5043,7 +4989,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -5054,67 +5000,67 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27">
         <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U27">
         <v>100</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5173,13 +5119,13 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T28">
         <v>100</v>
       </c>
       <c r="U28">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5232,7 +5178,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5247,7 +5193,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V29">
         <v>96.90000000000001</v>
@@ -5315,7 +5261,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5383,7 +5329,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -5436,7 +5382,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Q32">
         <v>97.5</v>
@@ -5445,13 +5391,13 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T32">
         <v>100</v>
       </c>
       <c r="U32">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -5520,30 +5466,30 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>79.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>17.2</v>
+        <v>6.9</v>
       </c>
       <c r="H2">
         <v>7.4</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5552,30 +5498,30 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>82.8</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5584,51 +5530,51 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>29</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5639,66 +5585,66 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>29</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>29</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5712,25 +5658,25 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5740,7 +5686,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5767,126 +5713,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920326</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920326</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920326</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920326</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920326</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920326</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5894,7 +5720,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5929,19 +5755,19 @@
         <v>22330051920010</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5949,16 +5775,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920010</v>
+        <v>22330051920013</v>
       </c>
       <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
         <v>67</v>
       </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5967,259 +5793,6 @@
         <v>54</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920010</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920010</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920003</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920003</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920006</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920006</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920015</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920015</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920013</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920017</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920382</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>
